--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
   <si>
     <t>id</t>
   </si>
@@ -203,6 +203,9 @@
     <t>可转生为人类</t>
   </si>
   <si>
+    <t>奖励-可获取人类装备</t>
+  </si>
+  <si>
     <t>解锁种族：骷髅</t>
   </si>
   <si>
@@ -227,6 +230,9 @@
     <t>可转生为骷髅</t>
   </si>
   <si>
+    <t>奖励-可获取骷髅装备</t>
+  </si>
+  <si>
     <t>解锁种族：史莱姆</t>
   </si>
   <si>
@@ -251,6 +257,9 @@
     <t>可转生为史莱姆</t>
   </si>
   <si>
+    <t>奖励-可获取史莱姆装备</t>
+  </si>
+  <si>
     <t>解锁种族：魅魔</t>
   </si>
   <si>
@@ -278,6 +287,9 @@
     <t>可转生为魅魔</t>
   </si>
   <si>
+    <t>奖励-可获取魅魔装备</t>
+  </si>
+  <si>
     <t>解锁种族：牛头人</t>
   </si>
   <si>
@@ -302,6 +314,9 @@
     <t>可转生为牛头人</t>
   </si>
   <si>
+    <t>奖励-可获取牛头人装备</t>
+  </si>
+  <si>
     <t>解锁种族：哥布林</t>
   </si>
   <si>
@@ -323,6 +338,9 @@
     <t>可转生为哥布林</t>
   </si>
   <si>
+    <t>奖励-可获取哥布林装备</t>
+  </si>
+  <si>
     <t>解锁种族：兽人</t>
   </si>
   <si>
@@ -345,6 +363,9 @@
   </si>
   <si>
     <t>可转生兽人</t>
+  </si>
+  <si>
+    <t>奖励-可获取兽人装备</t>
   </si>
 </sst>
 </file>
@@ -960,11 +981,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1315,7 +1339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="33.75" customWidth="1"/>
@@ -1896,10 +1920,10 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53">
-        <v>300200000</v>
-      </c>
-      <c r="B53">
+      <c r="A53" s="1">
+        <v>300100301</v>
+      </c>
+      <c r="B53" s="2">
         <v>0</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -1908,7 +1932,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1919,7 +1943,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1930,7 +1954,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1941,7 +1965,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1952,7 +1976,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1963,7 +1987,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1973,8 +1997,8 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="1">
-        <v>300200201</v>
+      <c r="A60">
+        <v>300200102</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1985,7 +2009,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1995,30 +2019,30 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62">
-        <v>300300001</v>
+      <c r="A62" s="1">
+        <v>300200301</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63">
-        <v>300300002</v>
+      <c r="A63" s="1">
+        <v>300300000</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2029,7 +2053,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2040,7 +2064,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2051,7 +2075,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2061,63 +2085,63 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="1">
+      <c r="A68">
+        <v>300300101</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>300300102</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1">
         <v>300300201</v>
       </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="1">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1">
+        <v>300300301</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
         <v>300400000</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>300400001</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>300400002</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>300400003</v>
-      </c>
       <c r="B72">
         <v>0</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2128,7 +2152,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2139,7 +2163,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2150,7 +2174,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2160,30 +2184,30 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="1">
-        <v>300400201</v>
+      <c r="A77">
+        <v>300400005</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="1">
-        <v>300500000</v>
+      <c r="A78">
+        <v>300400101</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="1">
-        <v>300500001</v>
+      <c r="A79">
+        <v>300400102</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2194,40 +2218,40 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1">
-        <v>300500002</v>
+        <v>300400201</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1">
-        <v>300500003</v>
+        <v>300400301</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="1">
-        <v>300500004</v>
+        <v>300500000</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83">
-        <v>300500101</v>
+      <c r="A83" s="1">
+        <v>300500001</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2237,8 +2261,8 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84">
-        <v>300500102</v>
+      <c r="A84" s="1">
+        <v>300500002</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2249,29 +2273,29 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1">
-        <v>300500201</v>
+        <v>300500003</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="1">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="1">
-        <v>300600001</v>
+      <c r="A87">
+        <v>300500101</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2281,8 +2305,8 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="1">
-        <v>300600002</v>
+      <c r="A88">
+        <v>300500102</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2293,167 +2317,244 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="1">
-        <v>300600003</v>
+        <v>300500201</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1">
-        <v>300600004</v>
+        <v>300500301</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92">
-        <v>300600101</v>
+      <c r="A92" s="1">
+        <v>300600001</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93">
-        <v>300600102</v>
+      <c r="A93" s="1">
+        <v>300600002</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1">
-        <v>300600201</v>
+        <v>300600003</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>97</v>
+      <c r="C94" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1">
-        <v>300700000</v>
+        <v>300600004</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>98</v>
+      <c r="C95" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1">
-        <v>300700001</v>
+        <v>300600005</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="1">
-        <v>300700002</v>
+      <c r="A97">
+        <v>300600101</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="1">
-        <v>300700003</v>
+      <c r="A98">
+        <v>300600102</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1">
-        <v>300700004</v>
+        <v>300600201</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100">
-        <v>300700101</v>
+      <c r="A100" s="1">
+        <v>300600301</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101">
-        <v>300700102</v>
+      <c r="A101" s="1">
+        <v>300700000</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="1">
+        <v>300700001</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1">
+        <v>300700002</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1">
+        <v>300700003</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1">
+        <v>300700004</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>300700101</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>300700102</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1">
         <v>300700201</v>
       </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="119" ht="12" customHeight="1"/>
-    <row r="120" ht="12" customHeight="1"/>
-    <row r="121" ht="12" customHeight="1"/>
-    <row r="122" ht="12" customHeight="1"/>
-    <row r="123" ht="12" customHeight="1"/>
-    <row r="124" ht="12" customHeight="1"/>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1">
+        <v>300700301</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="125" ht="12" customHeight="1"/>
     <row r="126" ht="12" customHeight="1"/>
     <row r="127" ht="12" customHeight="1"/>
+    <row r="128" ht="12" customHeight="1"/>
+    <row r="129" ht="12" customHeight="1"/>
+    <row r="130" ht="12" customHeight="1"/>
+    <row r="131" ht="12" customHeight="1"/>
+    <row r="132" ht="12" customHeight="1"/>
+    <row r="133" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>魔法世界-等级10</t>
+  </si>
+  <si>
+    <t>开启孕育功能</t>
   </si>
   <si>
     <t>孕育可跳过</t>
@@ -1339,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="33.75" customWidth="1"/>
@@ -1690,18 +1693,18 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1712,7 +1715,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1723,7 +1726,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1734,7 +1737,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1745,7 +1748,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1756,7 +1759,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1766,19 +1769,19 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39">
+      <c r="A39" s="1">
+        <v>100403001</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>200000001</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40">
-        <v>200000030</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1789,7 +1792,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
       <c r="A41">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1800,7 +1803,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
       <c r="A42">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1811,7 +1814,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3">
       <c r="A43">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1822,7 +1825,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3">
       <c r="A44">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1831,31 +1834,31 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" ht="15" customHeight="1" spans="1:3">
       <c r="A45">
+        <v>200100004</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>300100000</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1">
-        <v>300100001</v>
-      </c>
       <c r="B46">
         <v>0</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="1">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1866,7 +1869,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1877,7 +1880,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1888,18 +1891,18 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1910,9 +1913,9 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1">
-        <v>300100201</v>
-      </c>
-      <c r="B52" s="1">
+        <v>300100102</v>
+      </c>
+      <c r="B52">
         <v>0</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -1921,9 +1924,9 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="1">
-        <v>300100301</v>
-      </c>
-      <c r="B53" s="2">
+        <v>300100201</v>
+      </c>
+      <c r="B53" s="1">
         <v>0</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -1931,10 +1934,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54">
-        <v>300200000</v>
-      </c>
-      <c r="B54">
+      <c r="A54" s="1">
+        <v>300100301</v>
+      </c>
+      <c r="B54" s="2">
         <v>0</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -1943,7 +1946,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1954,7 +1957,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1965,7 +1968,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1976,7 +1979,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1987,7 +1990,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1998,7 +2001,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -2008,8 +2011,8 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="1">
-        <v>300200201</v>
+      <c r="A61">
+        <v>300200102</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2020,7 +2023,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="1">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2031,7 +2034,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="1">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2041,19 +2044,19 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64">
-        <v>300300001</v>
+      <c r="A64" s="1">
+        <v>300300000</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2064,7 +2067,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2075,7 +2078,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2086,7 +2089,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2097,7 +2100,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2107,19 +2110,19 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="1">
-        <v>300300201</v>
+      <c r="A70">
+        <v>300300102</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2130,7 +2133,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2140,19 +2143,19 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73">
-        <v>300400001</v>
+      <c r="A73" s="1">
+        <v>300400000</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2163,7 +2166,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2174,7 +2177,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2185,7 +2188,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2196,7 +2199,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2207,7 +2210,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2217,19 +2220,19 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="1">
-        <v>300400201</v>
+      <c r="A80">
+        <v>300400102</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2240,7 +2243,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="1">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2251,18 +2254,18 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="1">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="1">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2273,7 +2276,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2284,7 +2287,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="1">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2294,8 +2297,8 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87">
-        <v>300500101</v>
+      <c r="A87" s="1">
+        <v>300500004</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2306,7 +2309,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2316,19 +2319,19 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="1">
-        <v>300500201</v>
+      <c r="A89">
+        <v>300500102</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2339,7 +2342,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2350,18 +2353,18 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="1">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2372,7 +2375,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2383,7 +2386,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2394,7 +2397,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2404,19 +2407,19 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97">
-        <v>300600101</v>
+      <c r="A97" s="1">
+        <v>300600005</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2426,19 +2429,19 @@
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="1">
-        <v>300600201</v>
+      <c r="A99">
+        <v>300600102</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>102</v>
+      <c r="C99" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2449,7 +2452,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2460,18 +2463,18 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="1">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="1">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2482,7 +2485,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="1">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2493,7 +2496,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="1">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2503,8 +2506,8 @@
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106">
-        <v>300700101</v>
+      <c r="A106" s="1">
+        <v>300700004</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2515,7 +2518,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2525,19 +2528,19 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="1">
-        <v>300700201</v>
+      <c r="A108">
+        <v>300700102</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2546,7 +2549,17 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" ht="12" customHeight="1"/>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1">
+        <v>300700301</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="126" ht="12" customHeight="1"/>
     <row r="127" ht="12" customHeight="1"/>
     <row r="128" ht="12" customHeight="1"/>
@@ -2555,6 +2568,7 @@
     <row r="131" ht="12" customHeight="1"/>
     <row r="132" ht="12" customHeight="1"/>
     <row r="133" ht="12" customHeight="1"/>
+    <row r="134" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1195,1313 +1195,1326 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
+      <c r="A11" t="n">
+        <v>100100002</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>100300001</v>
+        <v>100200003</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>100300010</v>
+        <v>100300001</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>100310101</v>
+        <v>100300010</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>100310102</v>
+        <v>100310101</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>100310112</v>
+        <v>100310102</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>100310120</v>
+        <v>100310112</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>100310201</v>
+        <v>100310120</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100310202</v>
+        <v>100310201</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>100310212</v>
+        <v>100310202</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100310220</v>
+        <v>100310212</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100310301</v>
+        <v>100310220</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100310302</v>
+        <v>100310301</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100310312</v>
+        <v>100310302</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310320</v>
+        <v>100310312</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310401</v>
+        <v>100310320</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310402</v>
+        <v>100310401</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310412</v>
+        <v>100310402</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310420</v>
+        <v>100310412</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100400000</v>
+        <v>100310420</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>300100000</v>
+        <v>200100004</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
         <v>300700301</v>
       </c>
-      <c r="B110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="112">
+      <c r="A112" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="inlineStr">
+      <c r="B112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1195,1326 +1195,1352 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="2" t="n">
         <v>100100002</v>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
+      <c r="A12" t="n">
+        <v>100100003</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>终焉议会议案：魔物重命名</t>
+      <c r="A13" t="n">
+        <v>100100004</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>100300010</v>
+        <v>100200003</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>100310101</v>
+        <v>100300001</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>100310102</v>
+        <v>100300010</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>100310112</v>
+        <v>100310101</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>100310120</v>
+        <v>100310102</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100310201</v>
+        <v>100310112</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>100310202</v>
+        <v>100310120</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100310212</v>
+        <v>100310201</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100310220</v>
+        <v>100310202</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100310301</v>
+        <v>100310212</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100310302</v>
+        <v>100310220</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310312</v>
+        <v>100310301</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310320</v>
+        <v>100310302</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310401</v>
+        <v>100310312</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310402</v>
+        <v>100310320</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310412</v>
+        <v>100310401</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310420</v>
+        <v>100310402</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100400000</v>
+        <v>100310412</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100400001</v>
+        <v>100310420</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>200000001</v>
+        <v>100403000</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>200000030</v>
+        <v>100403001</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>200100002</v>
+        <v>200000030</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>200100003</v>
+        <v>200100001</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>200100004</v>
+        <v>200100002</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>300100000</v>
+        <v>200100003</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>300100001</v>
+        <v>200100004</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1208,26 +1208,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>100100003</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>100100004</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>不同魔物献祭成功率提升</t>
         </is>
@@ -1690,857 +1690,896 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>300100000</v>
+        <v>200200001</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>300100001</v>
+        <v>200300001</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>300100002</v>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>解锁职业：人类弓箭手</t>
+      <c r="A51" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>300100003</v>
+        <v>300100000</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>300100101</v>
+        <v>300100002</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>300100201</v>
+        <v>300100004</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>300200000</v>
+        <v>300100102</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300200001</v>
+        <v>300100201</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300200002</v>
+        <v>300100301</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>300200003</v>
+        <v>300200000</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300200101</v>
+        <v>300200002</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300200201</v>
+        <v>300200004</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300200301</v>
+        <v>300200101</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300300001</v>
+        <v>300200201</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300300002</v>
+        <v>300200301</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300300003</v>
+        <v>300300000</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300300101</v>
+        <v>300300002</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300300201</v>
+        <v>300300004</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300400001</v>
+        <v>300300201</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300400002</v>
+        <v>300300301</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300400201</v>
+        <v>300400005</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300500001</v>
+        <v>300400201</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300500002</v>
+        <v>300400301</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300500101</v>
+        <v>300500002</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300500201</v>
+        <v>300500004</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300600001</v>
+        <v>300500201</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300600002</v>
+        <v>300500301</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300600101</v>
+        <v>300600003</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300600201</v>
+        <v>300600005</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300700001</v>
+        <v>300600201</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300700002</v>
+        <v>300600301</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300700101</v>
+        <v>300700002</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300700201</v>
+        <v>300700004</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1287,1299 +1287,1364 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>100300010</v>
+        <v>100300002</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>100310101</v>
+        <v>100300003</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>100310102</v>
+        <v>100300004</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100310112</v>
+        <v>100300005</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>100310120</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级10</t>
+      <c r="A22" t="n">
+        <v>100300006</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100310201</v>
+        <v>100300010</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100310202</v>
+        <v>100310101</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100310212</v>
+        <v>100310102</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100310220</v>
+        <v>100310112</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310301</v>
+        <v>100310120</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310302</v>
+        <v>100310201</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310312</v>
+        <v>100310202</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310320</v>
+        <v>100310212</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310401</v>
+        <v>100310220</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310402</v>
+        <v>100310301</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310412</v>
+        <v>100310302</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310420</v>
+        <v>100310312</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100400000</v>
+        <v>100310320</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100400001</v>
+        <v>100310401</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100401000</v>
+        <v>100310402</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100401001</v>
+        <v>100310412</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100402000</v>
+        <v>100310420</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100402001</v>
+        <v>100400000</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100403000</v>
+        <v>100400001</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100403001</v>
+        <v>100401000</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>200000001</v>
+        <v>100401001</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>200000030</v>
+        <v>100402000</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>200100001</v>
+        <v>100402001</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>200100002</v>
+        <v>100403000</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>200100003</v>
+        <v>100403001</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>200100004</v>
+        <v>200000001</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>200200001</v>
+        <v>200000030</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>200300001</v>
+        <v>200100001</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>200400001</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>魔王魔力恢复速度+1/s</t>
+      <c r="A51" s="2" t="n">
+        <v>200100002</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>300100000</v>
+        <v>200100003</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>300100001</v>
+        <v>200100004</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>300100002</v>
+        <v>200200001</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>300100003</v>
+        <v>200300001</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>300100004</v>
+        <v>200400001</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>300100102</v>
+        <v>300100001</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300100201</v>
+        <v>300100002</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300100301</v>
+        <v>300100003</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>300200000</v>
+        <v>300100004</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>300200001</v>
+        <v>300100101</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300200002</v>
+        <v>300100102</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300200003</v>
+        <v>300100201</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300200004</v>
+        <v>300100301</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300200101</v>
+        <v>300200000</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300200102</v>
+        <v>300200001</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300200201</v>
+        <v>300200002</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300200301</v>
+        <v>300200003</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300300000</v>
+        <v>300200004</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300300001</v>
+        <v>300200101</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300300002</v>
+        <v>300200102</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300300003</v>
+        <v>300200201</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300300004</v>
+        <v>300200301</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300300102</v>
+        <v>300300001</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300300201</v>
+        <v>300300002</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300300301</v>
+        <v>300300003</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300400000</v>
+        <v>300300004</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300400001</v>
+        <v>300300101</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300400002</v>
+        <v>300300102</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300400003</v>
+        <v>300300201</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300400004</v>
+        <v>300300301</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300400005</v>
+        <v>300400000</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300400101</v>
+        <v>300400001</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300400102</v>
+        <v>300400002</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300400201</v>
+        <v>300400003</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300400301</v>
+        <v>300400004</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300500000</v>
+        <v>300400005</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300500001</v>
+        <v>300400101</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300500002</v>
+        <v>300400102</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300500003</v>
+        <v>300400201</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300500004</v>
+        <v>300400301</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300500102</v>
+        <v>300500001</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300500201</v>
+        <v>300500002</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300500301</v>
+        <v>300500003</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300600001</v>
+        <v>300500101</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300600002</v>
+        <v>300500102</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300600003</v>
+        <v>300500201</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300600004</v>
+        <v>300500301</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300600101</v>
+        <v>300600001</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300600102</v>
+        <v>300600002</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300600201</v>
+        <v>300600003</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300600301</v>
+        <v>300600004</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300700000</v>
+        <v>300600005</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300700001</v>
+        <v>300600101</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300700002</v>
+        <v>300600102</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300700003</v>
+        <v>300600201</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300700004</v>
+        <v>300600301</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300700102</v>
+        <v>300700001</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300700201</v>
+        <v>300700002</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300700301</v>
+        <v>300700003</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="B122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1182,1469 +1182,1495 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>100100001</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>开启献祭设施</t>
+      <c r="A10" t="n">
+        <v>100000006</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>进阶增益范围预览</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>100100002</v>
+        <v>100100001</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>献祭祭品数量+1</t>
+          <t>开启献祭设施</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>100100003</v>
+        <v>100100002</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>献祭失败保底概率提升</t>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>100100004</v>
+        <v>100100003</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>不同魔物献祭成功率提升</t>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>100200001</v>
+        <v>100100004</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>100300001</v>
+        <v>100200003</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>100300004</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>传送门详情-路径长度预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
         <v>100300005</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>传送门详情-奖励预览</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>100300006</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100300010</v>
+        <v>100300006</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100310101</v>
+        <v>100300010</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100310102</v>
+        <v>100310101</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100310112</v>
+        <v>100310102</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310120</v>
+        <v>100310112</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310201</v>
+        <v>100310120</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310202</v>
+        <v>100310201</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310212</v>
+        <v>100310202</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310220</v>
+        <v>100310212</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310301</v>
+        <v>100310220</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310302</v>
+        <v>100310301</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310312</v>
+        <v>100310302</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310320</v>
+        <v>100310312</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310401</v>
+        <v>100310320</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310402</v>
+        <v>100310401</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310412</v>
+        <v>100310402</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310420</v>
+        <v>100310412</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100400000</v>
+        <v>100310420</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200200001</v>
+        <v>200100004</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>300100000</v>
+        <v>200400001</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>300100001</v>
+        <v>200500001</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1182,13 +1182,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>100000006</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>进阶增益范围预览</t>
         </is>
@@ -1196,1489 +1196,1538 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>100100001</v>
+        <v>100000007</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>开启献祭设施</t>
+          <t>进阶魔晶加速倍率+1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>100100002</v>
+        <v>100000008</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>献祭祭品数量+1</t>
+          <t>进阶素材可选数量+1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>100100003</v>
+        <v>100100001</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>献祭失败保底概率提升</t>
+          <t>开启献祭设施</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>100100004</v>
+        <v>100100002</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>不同魔物献祭成功率提升</t>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>100200001</v>
+        <v>100100003</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>100200002</v>
+        <v>100100004</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>100300002</v>
+        <v>100200003</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>100300003</v>
+        <v>100300001</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100300004</v>
+        <v>100300002</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>100300005</v>
+        <v>100300003</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-奖励预览</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100300006</v>
+        <v>100300004</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>传送门刷新次数</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100300010</v>
+        <v>100300005</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100310101</v>
+        <v>100300006</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100310102</v>
+        <v>100300010</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310112</v>
+        <v>100310101</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310120</v>
+        <v>100310102</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310201</v>
+        <v>100310112</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310202</v>
+        <v>100310120</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310212</v>
+        <v>100310201</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310220</v>
+        <v>100310202</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310301</v>
+        <v>100310212</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310302</v>
+        <v>100310220</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310312</v>
+        <v>100310301</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310320</v>
+        <v>100310302</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310401</v>
+        <v>100310312</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310402</v>
+        <v>100310320</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310412</v>
+        <v>100310401</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310420</v>
+        <v>100310402</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100400000</v>
+        <v>100310412</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100400001</v>
+        <v>100310420</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>200000001</v>
+        <v>100403000</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>200000030</v>
+        <v>100403001</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>200100002</v>
+        <v>200000030</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>200100003</v>
+        <v>200100001</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200100004</v>
+        <v>200100002</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200200001</v>
+        <v>200100003</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200300001</v>
+        <v>200100004</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200400001</v>
+        <v>200200001</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200500001</v>
+        <v>200300001</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>300100000</v>
+        <v>200400001</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>300100001</v>
+        <v>200500001</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>300100002</v>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>解锁职业：人类弓箭手</t>
+      <c r="A61" t="n">
+        <v>200600001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>300100003</v>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>解锁职业：人类魔法师（火）</t>
+      <c r="A62" t="n">
+        <v>200700001</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300100004</v>
+        <v>300100000</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300100101</v>
+        <v>300100001</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300100102</v>
+        <v>300100002</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300100201</v>
+        <v>300100003</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300100301</v>
+        <v>300100004</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300200000</v>
+        <v>300100101</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300200001</v>
+        <v>300100102</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300200002</v>
+        <v>300100201</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300200003</v>
+        <v>300100301</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300200004</v>
+        <v>300200000</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300200101</v>
+        <v>300200001</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300200102</v>
+        <v>300200002</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300200201</v>
+        <v>300200003</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300200301</v>
+        <v>300200004</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300300000</v>
+        <v>300200101</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300300001</v>
+        <v>300200102</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300300002</v>
+        <v>300200201</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300300003</v>
+        <v>300200301</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300300004</v>
+        <v>300300000</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300300101</v>
+        <v>300300001</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300300102</v>
+        <v>300300002</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300300201</v>
+        <v>300300003</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300300301</v>
+        <v>300300004</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300400000</v>
+        <v>300300101</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300400001</v>
+        <v>300300102</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300400002</v>
+        <v>300300201</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300400003</v>
+        <v>300300301</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300400004</v>
+        <v>300400000</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300400005</v>
+        <v>300400001</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300400101</v>
+        <v>300400002</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300400102</v>
+        <v>300400003</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300400201</v>
+        <v>300400004</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400301</v>
+        <v>300400005</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300500000</v>
+        <v>300400101</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300500001</v>
+        <v>300400102</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300500002</v>
+        <v>300400201</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300500003</v>
+        <v>300400301</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300500004</v>
+        <v>300500000</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300500101</v>
+        <v>300500001</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300500102</v>
+        <v>300500002</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300500201</v>
+        <v>300500003</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300500301</v>
+        <v>300500004</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300600000</v>
+        <v>300500101</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300600001</v>
+        <v>300500102</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300600002</v>
+        <v>300500201</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300600003</v>
+        <v>300500301</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300600004</v>
+        <v>300600000</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300600005</v>
+        <v>300600001</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300600101</v>
+        <v>300600002</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300600102</v>
+        <v>300600003</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300600201</v>
+        <v>300600004</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600301</v>
+        <v>300600005</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300700000</v>
+        <v>300600101</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300700001</v>
+        <v>300600102</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300700002</v>
+        <v>300600201</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300700003</v>
+        <v>300600301</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300700004</v>
+        <v>300700000</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300700101</v>
+        <v>300700001</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300700102</v>
+        <v>300700002</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300700201</v>
+        <v>300700003</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300700301</v>
+        <v>300700004</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="12" customHeight="1" s="3">
+      <c r="A126" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="12" customHeight="1" s="3">
+      <c r="A127" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="12" customHeight="1" s="3">
+      <c r="A128" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="B128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="12" customHeight="1" s="3"/>
-    <row r="127" ht="12" customHeight="1" s="3"/>
-    <row r="128" ht="12" customHeight="1" s="3"/>
     <row r="129" ht="12" customHeight="1" s="3"/>
     <row r="130" ht="12" customHeight="1" s="3"/>
     <row r="131" ht="12" customHeight="1" s="3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1312,1423 +1312,1435 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>传送门可选择世界+1</t>
+      <c r="A20" t="n">
+        <v>100200004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>征服通关获得声望</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-奖励预览</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>传送门刷新次数</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100300010</v>
+        <v>100300006</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100310101</v>
+        <v>100300010</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310102</v>
+        <v>100310101</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310112</v>
+        <v>100310102</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310120</v>
+        <v>100310112</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310201</v>
+        <v>100310120</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310202</v>
+        <v>100310201</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310212</v>
+        <v>100310202</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310220</v>
+        <v>100310212</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310301</v>
+        <v>100310220</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310302</v>
+        <v>100310301</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310312</v>
+        <v>100310302</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310320</v>
+        <v>100310312</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310401</v>
+        <v>100310320</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310402</v>
+        <v>100310401</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100310412</v>
+        <v>100310402</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100310420</v>
+        <v>100310412</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100400000</v>
+        <v>100310420</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200200001</v>
+        <v>200100004</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>魔王魔力恢复速度+1/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
         <v>200500001</v>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="62">
+      <c r="A62" s="2" t="n">
         <v>200600001</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="B62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>空格突进</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>200700001</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="12" customHeight="1" s="3">
+      <c r="A129" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="12" customHeight="1" s="3"/>
     <row r="130" ht="12" customHeight="1" s="3"/>
     <row r="131" ht="12" customHeight="1" s="3"/>
     <row r="132" ht="12" customHeight="1" s="3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1312,13 +1312,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>100200004</v>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>征服通关获得声望</t>
         </is>
@@ -1468,1282 +1468,1318 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>100310201</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>世界-虚空魔界</t>
+      <c r="A32" t="n">
+        <v>100310130</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>剑与魔法-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310202</v>
+        <v>100310201</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310212</v>
+        <v>100310202</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310220</v>
+        <v>100310212</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310301</v>
+        <v>100310220</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310302</v>
+        <v>100310301</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310312</v>
+        <v>100310302</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310320</v>
+        <v>100310312</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310401</v>
+        <v>100310320</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100310402</v>
+        <v>100310401</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100310412</v>
+        <v>100310402</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100310420</v>
+        <v>100310412</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100400000</v>
+        <v>100310420</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200200001</v>
+        <v>200100004</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>300100002</v>
+        <v>200900001</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300100003</v>
+        <v>300100000</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300100101</v>
+        <v>300100002</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300100201</v>
+        <v>300100004</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300200000</v>
+        <v>300100102</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300200001</v>
+        <v>300100201</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300200002</v>
+        <v>300100301</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300200003</v>
+        <v>300200000</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300200101</v>
+        <v>300200002</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300200201</v>
+        <v>300200004</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300200301</v>
+        <v>300200101</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300300001</v>
+        <v>300200201</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300300002</v>
+        <v>300200301</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300300003</v>
+        <v>300300000</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300300101</v>
+        <v>300300002</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300300201</v>
+        <v>300300004</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300400001</v>
+        <v>300300201</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300400002</v>
+        <v>300300301</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300400201</v>
+        <v>300400005</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300500001</v>
+        <v>300400201</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300500002</v>
+        <v>300400301</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300500101</v>
+        <v>300500002</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300500201</v>
+        <v>300500004</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300600001</v>
+        <v>300500201</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300600002</v>
+        <v>300500301</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300600101</v>
+        <v>300600003</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300600201</v>
+        <v>300600005</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300700001</v>
+        <v>300600201</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300700002</v>
+        <v>300600301</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300700101</v>
+        <v>300700002</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300700201</v>
+        <v>300700004</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="12" customHeight="1" s="3">
+      <c r="A130" s="2" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="12" customHeight="1" s="3">
+      <c r="A131" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="12" customHeight="1" s="3">
+      <c r="A132" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="12" customHeight="1" s="3"/>
-    <row r="131" ht="12" customHeight="1" s="3"/>
-    <row r="132" ht="12" customHeight="1" s="3"/>
     <row r="133" ht="12" customHeight="1" s="3"/>
     <row r="134" ht="12" customHeight="1" s="3"/>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1468,13 +1468,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="2" t="n">
         <v>100310130</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-加快进攻节奏</t>
         </is>
@@ -1741,1046 +1741,1058 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>200000001</v>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>阵容魔物上限+1</t>
+      <c r="A53" t="n">
+        <v>100600001</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>200200001</v>
+        <v>200100004</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>每次拾取魔晶+1</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300100000</v>
+        <v>200900001</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1" s="3">
       <c r="A130" s="2" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1" s="3">
       <c r="A131" s="2" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1" s="3">
       <c r="A132" s="2" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="12" customHeight="1" s="3">
+      <c r="A133" s="2" t="n">
         <v>100500001</v>
       </c>
-      <c r="B132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="12" customHeight="1" s="3"/>
     <row r="134" ht="12" customHeight="1" s="3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1741,13 +1741,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="2" t="n">
         <v>100600001</v>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>开启魔汁机</t>
         </is>
@@ -2793,7 +2793,19 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="12" customHeight="1" s="3"/>
+    <row r="134" ht="12" customHeight="1" s="3">
+      <c r="A134" t="n">
+        <v>100600002</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>魔汁机投入数量+1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1469,1340 +1469,1678 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310130</v>
+        <v>100310201</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-加快进攻节奏</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310201</v>
+        <v>100310202</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310202</v>
+        <v>100310212</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310212</v>
+        <v>100310220</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310220</v>
+        <v>100310301</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310301</v>
+        <v>100310302</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310302</v>
+        <v>100310312</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310312</v>
+        <v>100310320</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310320</v>
+        <v>100310401</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100310401</v>
+        <v>100310402</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100310402</v>
+        <v>100310412</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100310412</v>
+        <v>100310420</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100310420</v>
+        <v>100400000</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100400000</v>
+        <v>100400001</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100400001</v>
+        <v>100401000</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100401000</v>
+        <v>100401001</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100401001</v>
+        <v>100402000</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100402000</v>
+        <v>100402001</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100402001</v>
+        <v>100403000</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>100403000</v>
+        <v>100403001</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>100403001</v>
+        <v>100600001</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>100600001</v>
+        <v>200000001</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>开启魔汁机</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200000001</v>
+        <v>200000030</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200000030</v>
+        <v>200100001</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200100001</v>
+        <v>200100002</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200100002</v>
+        <v>200100003</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200100003</v>
+        <v>200100004</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>200100004</v>
+        <v>200200001</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>200200001</v>
+        <v>200300001</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>200300001</v>
+        <v>200400001</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>200400001</v>
+        <v>200500001</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>200500001</v>
+        <v>200600001</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>200900001</v>
+        <v>300100000</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>每次拾取魔晶+1</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300100000</v>
+        <v>300100001</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300100001</v>
+        <v>300100002</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300100002</v>
+        <v>300100003</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300100003</v>
+        <v>300100004</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300100004</v>
+        <v>300100101</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300100101</v>
+        <v>300100102</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300100102</v>
+        <v>300100201</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300100201</v>
+        <v>300100301</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300100301</v>
+        <v>300200000</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300200000</v>
+        <v>300200001</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300200001</v>
+        <v>300200002</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300200002</v>
+        <v>300200003</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300200003</v>
+        <v>300200004</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300200004</v>
+        <v>300200101</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300200101</v>
+        <v>300200102</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300200102</v>
+        <v>300200201</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300200201</v>
+        <v>300200301</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300200301</v>
+        <v>300300000</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300300000</v>
+        <v>300300001</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300300001</v>
+        <v>300300002</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300300002</v>
+        <v>300300003</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300300003</v>
+        <v>300300004</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300300004</v>
+        <v>300300101</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300300101</v>
+        <v>300300102</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300300102</v>
+        <v>300300201</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300300201</v>
+        <v>300300301</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300300301</v>
+        <v>300400000</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400000</v>
+        <v>300400001</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300400001</v>
+        <v>300400002</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300400002</v>
+        <v>300400003</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300400003</v>
+        <v>300400004</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300400004</v>
+        <v>300400005</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300400005</v>
+        <v>300400101</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300400101</v>
+        <v>300400102</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300400102</v>
+        <v>300400201</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300400301</v>
+        <v>300500000</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300500000</v>
+        <v>300500001</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300500001</v>
+        <v>300500002</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300500002</v>
+        <v>300500003</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300500003</v>
+        <v>300500004</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300500004</v>
+        <v>300500101</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300500101</v>
+        <v>300500102</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300500102</v>
+        <v>300500201</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300500201</v>
+        <v>300500301</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300500301</v>
+        <v>300600000</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600000</v>
+        <v>300600001</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300600001</v>
+        <v>300600002</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300600002</v>
+        <v>300600003</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300600003</v>
+        <v>300600004</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300600004</v>
+        <v>300600005</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300600005</v>
+        <v>300600101</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300600101</v>
+        <v>300600102</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300600102</v>
+        <v>300600201</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300600201</v>
+        <v>300600301</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300600301</v>
+        <v>300700000</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300700000</v>
+        <v>300700001</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300700001</v>
+        <v>300700002</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300700002</v>
+        <v>300700003</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300700003</v>
+        <v>300700004</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300700004</v>
+        <v>300700101</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
-        <v>300700101</v>
+        <v>300700102</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1" s="3">
       <c r="A130" s="2" t="n">
-        <v>300700102</v>
+        <v>300700201</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1" s="3">
       <c r="A131" s="2" t="n">
-        <v>300700201</v>
+        <v>300700301</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1" s="3">
       <c r="A132" s="2" t="n">
-        <v>300700301</v>
+        <v>100500001</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>开启成就系统</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1" s="3">
       <c r="A133" s="2" t="n">
-        <v>100500001</v>
+        <v>100600002</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>开启成就系统</t>
+          <t>魔汁机投入数量+1</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1" s="3">
-      <c r="A134" t="n">
-        <v>100600002</v>
-      </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>魔汁机投入数量+1</t>
+      <c r="A134" s="2" t="n">
+        <v>100310113</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>100310114</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>100310115</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>100310116</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>100310117</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>100310118</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>100310119</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-等级9</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>100310131</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度2-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>100310132</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度3-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>100310133</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>100310134</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>100310135</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>100310136</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>100310137</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>100310138</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>100310139</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>100310130</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度1-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>100310140</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度1-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>100310141</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度2-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>100310142</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度3-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>100310143</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>100310144</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>100310145</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>100310146</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>100310147</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>100310148</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>100310149</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-2倍速游戏</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -3015,132 +3015,184 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" s="2" t="n">
         <v>100310140</v>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="B151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度1-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" s="2" t="n">
         <v>100310141</v>
       </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="inlineStr">
+      <c r="B152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度2-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" s="2" t="n">
         <v>100310142</v>
       </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="inlineStr">
+      <c r="B153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度3-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" s="2" t="n">
         <v>100310143</v>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="B154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度4-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" s="2" t="n">
         <v>100310144</v>
       </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" t="inlineStr">
+      <c r="B155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度5-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" s="2" t="n">
         <v>100310145</v>
       </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" t="inlineStr">
+      <c r="B156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度6-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" s="2" t="n">
         <v>100310146</v>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" t="inlineStr">
+      <c r="B157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度7-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" s="2" t="n">
         <v>100310147</v>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="inlineStr">
+      <c r="B158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度8-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" s="2" t="n">
         <v>100310148</v>
       </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度9-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" s="2" t="n">
         <v>100310149</v>
       </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-难度10-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>100200005</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>终焉议会议案：魔物等级下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>100200006</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>终焉议会议案：魔物等级归0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>100200007</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>终焉议会议案：魔物稀有度下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>100200008</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>终焉议会议案：魔物稀有度归0</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -3145,54 +3145,80 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="2" t="n">
         <v>100200005</v>
       </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物等级下降</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" s="2" t="n">
         <v>100200006</v>
       </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
-      <c r="C162" t="inlineStr">
+      <c r="B162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物等级归0</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" s="2" t="n">
         <v>100200007</v>
       </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="B163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物稀有度下降</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" s="2" t="n">
         <v>100200008</v>
       </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" t="inlineStr">
+      <c r="B164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物稀有度归0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>100200009</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>终焉议会议案：想要更多装备！</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>100200010</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>终焉议会议案：想要更多魔王装备！</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -3210,15 +3210,28 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" s="2" t="n">
         <v>100200010</v>
       </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" t="inlineStr">
+      <c r="B166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>终焉议会议案：想要更多魔王装备！</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>201000001</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>阵容重命名</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1326,1912 +1326,3082 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>100300001</v>
+        <v>100200005</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔物等级下降</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>100300002</v>
+        <v>100200006</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>终焉议会议案：魔物等级归0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>100300003</v>
+        <v>100200007</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>终焉议会议案：魔物稀有度下降</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100300004</v>
+        <v>100200008</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>终焉议会议案：魔物稀有度归0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>100300005</v>
+        <v>100200009</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-奖励预览</t>
+          <t>终焉议会议案：想要更多装备！</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>100300006</v>
+        <v>100200010</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>传送门刷新次数</t>
+          <t>终焉议会议案：想要更多魔王装备！</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>100300010</v>
+        <v>100300001</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100310101</v>
+        <v>100300002</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100310102</v>
+        <v>100300003</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100310112</v>
+        <v>100300004</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100310120</v>
+        <v>100300005</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100310201</v>
+        <v>100300006</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100310202</v>
+        <v>100300010</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310212</v>
+        <v>100310101</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310220</v>
+        <v>100310102</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>剑与魔法-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310301</v>
+        <v>100310112</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310302</v>
+        <v>100310113</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>剑与魔法-等级3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310312</v>
+        <v>100310114</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>剑与魔法-等级4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310320</v>
+        <v>100310115</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>剑与魔法-等级5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310401</v>
+        <v>100310116</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>剑与魔法-等级6</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100310402</v>
+        <v>100310117</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>剑与魔法-等级7</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100310412</v>
+        <v>100310118</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>剑与魔法-等级8</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100310420</v>
+        <v>100310119</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>剑与魔法-等级9</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100400000</v>
+        <v>100310120</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100400001</v>
+        <v>100310130</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>剑与魔法-难度1-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100401000</v>
+        <v>100310131</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>剑与魔法-难度2-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100401001</v>
+        <v>100310132</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>剑与魔法-难度3-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100402000</v>
+        <v>100310133</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>剑与魔法-难度4-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100402001</v>
+        <v>100310134</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>剑与魔法-难度5-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100403000</v>
+        <v>100310135</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>剑与魔法-难度6-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>100403001</v>
+        <v>100310136</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>剑与魔法-难度7-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>100600001</v>
+        <v>100310137</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>开启魔汁机</t>
+          <t>剑与魔法-难度8-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>200000001</v>
+        <v>100310138</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>剑与魔法-难度9-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>200000030</v>
+        <v>100310139</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>剑与魔法-难度10-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>200100001</v>
+        <v>100310140</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>剑与魔法-难度1-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>200100002</v>
+        <v>100310141</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>剑与魔法-难度2-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>200100003</v>
+        <v>100310142</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>剑与魔法-难度3-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>200100004</v>
+        <v>100310143</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>剑与魔法-难度4-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>200200001</v>
+        <v>100310144</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>剑与魔法-难度5-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>200300001</v>
+        <v>100310145</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>剑与魔法-难度6-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>200400001</v>
+        <v>100310146</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>剑与魔法-难度7-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>200500001</v>
+        <v>100310147</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>剑与魔法-难度8-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>200600001</v>
+        <v>100310148</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>剑与魔法-难度9-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>200700001</v>
+        <v>100310149</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>剑与魔法-难度10-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>200800001</v>
+        <v>100310201</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>200900001</v>
+        <v>100310202</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>每次拾取魔晶+1</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>300100000</v>
+        <v>100310212</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>300100001</v>
+        <v>100310220</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>300100002</v>
+        <v>100310301</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>300100003</v>
+        <v>100310302</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>300100004</v>
+        <v>100310312</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>300100101</v>
+        <v>100310320</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>300100102</v>
+        <v>100310401</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>300100201</v>
+        <v>100310402</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>300100301</v>
+        <v>100310412</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>300200000</v>
+        <v>100310420</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>300200001</v>
+        <v>100400000</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>300200002</v>
+        <v>100400001</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>300200003</v>
+        <v>100401000</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>300200004</v>
+        <v>100401001</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>300200101</v>
+        <v>100402000</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>300200102</v>
+        <v>100402001</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>300200201</v>
+        <v>100403000</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>300200301</v>
+        <v>100403001</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>300300000</v>
+        <v>100500001</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>开启成就系统</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>300300001</v>
+        <v>100600001</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>300300002</v>
+        <v>100600002</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>魔汁机投入数量+1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>300300003</v>
+        <v>200000001</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>300300004</v>
+        <v>200000030</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>300300101</v>
+        <v>200100001</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>300300102</v>
+        <v>200100002</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>300300201</v>
+        <v>200100003</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>300300301</v>
+        <v>200100004</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>300400000</v>
+        <v>200200001</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>300400001</v>
+        <v>200300001</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>300400002</v>
+        <v>200400001</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>300400003</v>
+        <v>200500001</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>300400004</v>
+        <v>200600001</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>300400005</v>
+        <v>200700001</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>300400101</v>
+        <v>200800001</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>300400102</v>
+        <v>200900001</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>300400201</v>
+        <v>201000001</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>阵容重命名</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300400301</v>
+        <v>300100000</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300500000</v>
+        <v>300100001</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300500001</v>
+        <v>300100002</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300500002</v>
+        <v>300100003</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300500003</v>
+        <v>300100004</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300500004</v>
+        <v>300100101</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300500101</v>
+        <v>300100102</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300500102</v>
+        <v>300100201</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300500201</v>
+        <v>300100301</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300500301</v>
+        <v>300110011</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育人类战士x1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300600000</v>
+        <v>300110012</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育人类战士x5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300600001</v>
+        <v>300110013</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育人类战士x10</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300600002</v>
+        <v>300110021</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育人类弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300600003</v>
+        <v>300110022</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>孕育人类弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300600004</v>
+        <v>300110023</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>孕育人类弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300600005</v>
+        <v>300110031</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>孕育人类魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300600101</v>
+        <v>300110032</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育人类魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300600102</v>
+        <v>300110033</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育人类魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300600201</v>
+        <v>300110041</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育人类魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300600301</v>
+        <v>300110042</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育人类魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300700000</v>
+        <v>300110043</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育人类魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300700001</v>
+        <v>300200000</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300700002</v>
+        <v>300200001</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300700003</v>
+        <v>300200002</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300700004</v>
+        <v>300200003</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300700101</v>
+        <v>300200004</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
-        <v>300700102</v>
+        <v>300200101</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1" s="3">
       <c r="A130" s="2" t="n">
-        <v>300700201</v>
+        <v>300200102</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1" s="3">
       <c r="A131" s="2" t="n">
-        <v>300700301</v>
+        <v>300200201</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1" s="3">
       <c r="A132" s="2" t="n">
-        <v>100500001</v>
+        <v>300200301</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>开启成就系统</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1" s="3">
       <c r="A133" s="2" t="n">
-        <v>100600002</v>
+        <v>300210011</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>魔汁机投入数量+1</t>
+          <t>孕育骷髅战士x1</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1" s="3">
       <c r="A134" s="2" t="n">
-        <v>100310113</v>
+        <v>300210012</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级3</t>
+          <t>孕育骷髅战士x5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>100310114</v>
+        <v>300210013</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级4</t>
+          <t>孕育骷髅战士x10</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>100310115</v>
+        <v>300210021</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级5</t>
+          <t>孕育骷髅投手x1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>100310116</v>
+        <v>300210022</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级6</t>
+          <t>孕育骷髅投手x5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>100310117</v>
+        <v>300210023</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级7</t>
+          <t>孕育骷髅投手x10</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>100310118</v>
+        <v>300210031</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级8</t>
+          <t>孕育骷髅魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>100310119</v>
+        <v>300210032</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级9</t>
+          <t>孕育骷髅魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>100310131</v>
+        <v>300210033</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-加快进攻节奏</t>
+          <t>孕育骷髅魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>100310132</v>
+        <v>300210041</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-加快进攻节奏</t>
+          <t>孕育骷髅魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>100310133</v>
+        <v>300210042</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-加快进攻节奏</t>
+          <t>孕育骷髅魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>100310134</v>
+        <v>300210043</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-加快进攻节奏</t>
+          <t>孕育骷髅魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>100310135</v>
+        <v>300300000</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-加快进攻节奏</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>100310136</v>
+        <v>300300001</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-加快进攻节奏</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>100310137</v>
+        <v>300300002</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-加快进攻节奏</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>100310138</v>
+        <v>300300003</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-加快进攻节奏</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>100310139</v>
+        <v>300300004</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-加快进攻节奏</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>100310130</v>
+        <v>300300101</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-加快进攻节奏</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>100310140</v>
+        <v>300300102</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-2倍速游戏</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>100310141</v>
+        <v>300300201</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-2倍速游戏</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>100310142</v>
+        <v>300300301</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-2倍速游戏</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>100310143</v>
+        <v>300310011</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-2倍速游戏</t>
+          <t>孕育守护史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>100310144</v>
+        <v>300310012</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-2倍速游戏</t>
+          <t>孕育守护史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>100310145</v>
+        <v>300310013</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-2倍速游戏</t>
+          <t>孕育守护史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>100310146</v>
+        <v>300310021</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-2倍速游戏</t>
+          <t>孕育自爆史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>100310147</v>
+        <v>300310022</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-2倍速游戏</t>
+          <t>孕育自爆史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>100310148</v>
+        <v>300310023</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-2倍速游戏</t>
+          <t>孕育自爆史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>100310149</v>
+        <v>300310031</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-2倍速游戏</t>
+          <t>孕育烂泥史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>100200005</v>
+        <v>300310032</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物等级下降</t>
+          <t>孕育烂泥史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>100200006</v>
+        <v>300310033</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物等级归0</t>
+          <t>孕育烂泥史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>100200007</v>
+        <v>300310041</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物稀有度下降</t>
+          <t>孕育毒液史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>100200008</v>
+        <v>300310042</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物稀有度归0</t>
+          <t>孕育毒液史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>100200009</v>
+        <v>300310043</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：想要更多装备！</t>
+          <t>孕育毒液史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>100200010</v>
+        <v>300400000</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>终焉议会议案：想要更多魔王装备！</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
-        <v>201000001</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>阵容重命名</t>
+      <c r="A167" s="2" t="n">
+        <v>300400001</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>解锁职业：战之魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>300400002</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>解锁职业：愈之魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>300400003</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>解锁职业：惑之魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>300400004</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>解锁职业：奥之魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>300400005</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>解锁职业：盾之魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>300400101</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>孕育魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>孕育魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>300400201</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>可转生为魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>300400301</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>奖励-可获取魅魔装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>300410011</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>孕育战之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>300410012</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>孕育战之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>300410013</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>孕育战之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>300410021</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>孕育愈之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>300410022</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>孕育愈之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>300410023</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>孕育愈之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>300410031</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>孕育惑之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>300410032</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>孕育惑之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>300410033</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>孕育惑之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>300410041</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>孕育奥之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>300410042</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>孕育奥之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>300410043</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>孕育奥之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>300410051</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>孕育盾之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>300410052</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>孕育盾之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>300410053</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>孕育盾之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>300500000</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>解锁种族：牛头人</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>300500001</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>300500002</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人投手</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>300500003</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人魔法师（火）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>300500004</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>300500101</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>孕育牛头人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>孕育牛头人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>300500201</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>可转生为牛头人</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>300500301</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>奖励-可获取牛头人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>300510011</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>孕育牛头人战士x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>300510012</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>孕育牛头人战士x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>300510013</v>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>孕育牛头人战士x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>300510021</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>孕育牛头人投手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>300510022</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>孕育牛头人投手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>300510023</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>孕育牛头人投手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>300510031</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>300510032</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>300510033</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>300510041</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>300510042</v>
+      </c>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>300510043</v>
+      </c>
+      <c r="B211" t="n">
+        <v>0</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>孕育牛头人魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>300600000</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>解锁种族：哥布林</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>300600001</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林刺客</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>300600002</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林弓箭手</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>300600003</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林敢死队</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>300600004</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林魔法师（火）</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>300600005</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>300600101</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>孕育魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>孕育魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>300600201</v>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>可转生为哥布林</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>300600301</v>
+      </c>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>奖励-可获取哥布林装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>300610011</v>
+      </c>
+      <c r="B222" t="n">
+        <v>0</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>孕育哥布林刺客x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>300610012</v>
+      </c>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>孕育哥布林刺客x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>300610013</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>孕育哥布林刺客x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>300610021</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>孕育哥布林弓箭手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>300610022</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>孕育哥布林弓箭手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>300610023</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>孕育哥布林弓箭手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>300610031</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>孕育哥布林敢死队x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>300610032</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>孕育哥布林敢死队x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>300610033</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>孕育哥布林敢死队x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>300610041</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>300610042</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>300610043</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>300610051</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>300610052</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>300610053</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>孕育哥布林魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>解锁种族：兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>300700001</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>300700002</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人弓箭手</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>300700003</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（火）</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>300710011</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>孕育兽人战士x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>300710012</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>孕育兽人战士x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>300710013</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>孕育兽人战士x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>300710021</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>300710022</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>300710023</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>300710031</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>300710032</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>300710033</v>
+      </c>
+      <c r="B254" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>300710041</v>
+      </c>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>300710042</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>300710043</v>
+      </c>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
